--- a/public/business-plans/healthcare.xlsx
+++ b/public/business-plans/healthcare.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,10 @@
       <sz val="13"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
     <font>
@@ -66,12 +70,17 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -115,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,19 +133,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -558,10 +570,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Здравоохранение и социальные услуги». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
+          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Здравоохранение и социальные услуги». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Абзацы, отмеченные как «ПРИМЕР», — иллюстрация формата ответа, а не факты о реальной компании; замените их своими данными. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
         </is>
       </c>
     </row>
@@ -579,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -592,31 +604,39 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Медицинский центр «Salomatlik Plus» открывает многопрофильную поликлинику с УЗИ-диагностикой в растущем спальном районе Ташкента. Требуемые инвестиции — 2,4 млрд сум на оборудование и ремонт помещения под медицинские стандарты; окупаемость — около 30 месяцев при выходе на 40 приёмов в день.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] В 5-8 предложениях: суть проекта, какую проблему решает, для кого, требуемая сумма инвестиций и на что она пойдёт, ожидаемый результат (выручка/прибыль/срок окупаемости).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Описание компании / проекта</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Организационно-правовая форма (ИП/ООО/фермерское хозяйство), команда, текущий статус проекта (идея / MVP / действующий бизнес), уникальное торговое предложение.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -628,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -641,70 +661,94 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="59" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>•  Растёт спрос на качественные частные медицинские услуги в крупных городах Узбекистана.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
+          <t>•  Растёт спрос на качественные платные медицинские услуги: по данным Upl.uz со ссылкой на официальную статистику, за январь–август 2025 года объём рынка платных медицинских услуг Узбекистана составил 12,7 трлн сум с ростом на 12,6% год к году (upl.uz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="74" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>•  Развивается медицинский туризм из соседних стран для отдельных видов услуг.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+          <t>•  Рынок сильно централизован в столице: на Ташкент пришлось около половины всего объёма (5,9 трлн сум), далее — Ташкентская область (1,3 трлн сум) и Самаркандская область (938,4 млрд сум); наименьшие объёмы — в Навоийской, Сырдарьинской областях и Каракалпакстане (upl.uz) — в менее насыщенных регионах конкуренция ниже, но и платёжеспособный спрос меньше.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>•  Медицинская деятельность подлежит обязательному лицензированию Министерством здравоохранения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>•  Число частных медицинских учреждений в стране продолжает расти год к году (по данным Госкомстата) — сектор активно переходит от единичных кабинетов к сетевым многопрофильным клиникам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="59" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>•  [Впишите] Специализацию центра, конкурентов и их загрузку в вашем регионе.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+          <t>•  Развивается медицинский туризм из соседних стран для отдельных видов услуг (стоматология, пластическая хирургия, отдельные виды диагностики) — но эта ниша требует международной сертификации и маркетинга за пределами Узбекистана.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="59" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>•  Медицинская деятельность подлежит обязательному лицензированию Министерством здравоохранения — сроки и требования лицензирования стоит закладывать в план запуска заранее, это не быстрый процесс.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="74" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>•  Для сравнения: в Казахстане и России частная медицина более консолидирована в сетевые бренды с развитой страховой моделью оплаты — в Узбекистане доля оплаты услуг напрямую пациентом (а не через страховку) всё ещё выше, что делает ценовую доступность более значимым фактором выбора клиники для пациента.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>•  [Впишите] Специализацию центра, конкурентов и их загрузку в вашем регионе — уточняйте по данным местного управления здравоохранения и отзывам пациентов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Конкуренты</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Целевая аудитория</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Портрет основного клиента: кто он, что для него важно при выборе, где его найти.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -716,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -729,117 +773,183 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цена — среднерыночная для сегмента с прозрачным прайс-листом на сайте; продвижение — партнёрство с работодателями района на корпоративные программы чек-апов, отзывы пациентов на агрегаторах, контент о профилактике в соцсетях для формирования доверия к центру.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Ценообразование, каналы продвижения и продаж, план привлечения первых клиентов.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Операционный план</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5" ht="74" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цикл: запись пациента → приём/консультация → при необходимости диагностика на месте → назначение и, при необходимости, повторный приём → ведение медицинской карты. Требуется лицензирование Минздрава на каждый вид медицинской деятельности и наём персонала с действующими сертификатами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Процесс производства/оказания услуги, ключевые поставщики, оборудование, необходимые лицензии и разрешения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Организационный план</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>Организационный план</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="59" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Главный врач-совладелец, 4 врача разных специализаций, 2 медсестры, администратор ресепшена, бухгалтер на аутсорсе. Форма — ООО с лицензией на медицинскую деятельность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Риски и меры по их снижению (примеры для отрасли)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Риск</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Меры снижения</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Дефицит квалифицированных врачей</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Конкурентные условия, партнёрства с мед. вузами</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Регуляторные требования и лицензирование</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Своевременное соответствие стандартам Минздрава</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Репутационные риски</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Контроль качества услуг, работа с отзывами пациентов</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Дефицит квалифицированных врачей нужной специализации</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Конкурентные условия, партнёрства с медицинскими вузами, программы наставничества</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Регуляторные требования и длительные сроки лицензирования</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Заблаговременная подготовка документов, консультации с профильными юристами до старта</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="59" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Репутационные риски при врачебных ошибках или жалобах пациентов</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Контроль качества услуг, страхование профессиональной ответственности, прозрачная работа с жалобами</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Высокая концентрация конкурентов в крупных городах</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Чёткая специализация и УТП, рассмотрение менее насыщенных районов/регионов</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Рост цен на медицинское оборудование и расходники (валютная составляющая)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Долгосрочные контракты с поставщиками, частичное резервирование в валюте</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="59" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Отток пациентов к медтуризму за рубеж по сложным случаям</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Партнёрства с зарубежными клиниками для сложных случаев, фокус на массовые и профилактические услуги на месте</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>[Впишите] Дополните таблицу своими рисками, специфичными для вашего проекта и региона.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="21">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -851,316 +961,346 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Сумма, сум</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Добавляйте свои строки при необходимости.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Ремонт и оснащение помещения под мед. стандарты</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Медицинское оборудование</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="B8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Лицензирование медицинской деятельности</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="B9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Найм квалифицированного персонала</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="B10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>IT-система учёта пациентов</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="B11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="21" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
+          <t>Страхование профессиональной ответственности</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>часто требуется на этапе лицензирования</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
           <t>Итого: стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B12" s="15">
-        <f>SUM(B7:B11)</f>
+      <c r="B13" s="16">
+        <f>SUM(B7:B12)</f>
         <v/>
       </c>
-      <c r="C12" s="16" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="C13" s="17" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Приём и консультации</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="B16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Диагностические услуги</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="B17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Программы / абонементы</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="B18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>чек-апы, ведение хронических пациентов</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Корпоративные программы для работодателей</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>профилактические осмотры сотрудников</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B18" s="15">
-        <f>SUM(B15:B17)</f>
+      <c r="B20" s="16">
+        <f>SUM(B16:B19)</f>
         <v/>
       </c>
-      <c r="C18" s="16" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="C20" s="17" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>ФОТ врачей и мед. персонала</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="B23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Расходные материалы и медикаменты</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="B24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Обслуживание оборудования</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="B25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Аренда и коммунальные услуги</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Страхование профессиональной ответственности</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="B27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B26" s="15">
-        <f>SUM(B21:B25)</f>
+      <c r="B28" s="16">
+        <f>SUM(B23:B27)</f>
         <v/>
       </c>
-      <c r="C26" s="16" t="n"/>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Ежемесячная прибыль</t>
-        </is>
-      </c>
-      <c r="B28" s="10">
-        <f>B18-B26</f>
-        <v/>
-      </c>
+      <c r="C28" s="17" t="n"/>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Ежемесячная прибыль</t>
+        </is>
+      </c>
+      <c r="B30" s="11">
+        <f>B20-B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Срок выхода на окупаемость, мес.</t>
         </is>
       </c>
-      <c r="B30" s="13">
-        <f>IFERROR(B4/B28,"—")</f>
+      <c r="B32" s="14">
+        <f>IFERROR(B4/B30,"—")</f>
         <v/>
       </c>
-      <c r="C30" s="13">
+      <c r="C32" s="14">
         <f> Начальные инвестиции / Ежемесячная прибыль</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Рентабельность продаж, %</t>
         </is>
       </c>
-      <c r="B31" s="17">
-        <f>IFERROR(B28/B18*100,"—")</f>
+      <c r="B33" s="18">
+        <f>IFERROR(B30/B20*100,"—")</f>
         <v/>
       </c>
-      <c r="C31" s="13">
+      <c r="C33" s="14">
         <f> Ежемесячная прибыль / Выручка × 100%</f>
         <v/>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта.</t>
+    <row r="34"/>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/business-plans/healthcare.xlsx
+++ b/public/business-plans/healthcare.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
     </font>
   </fonts>
   <fills count="5">
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +126,9 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -498,14 +505,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ФИНАНСОВЫЙ ПЛАН: ЗДРАВООХРАНЕНИЕ И СОЦИАЛЬНЫЕ УСЛУГИ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
+          <t>ФИНАНСОВЫЙ ПЛАН: ЗДРАВООХРАНЕНИЕ И СОЦИАЛЬНЫЕ УСЛУГИ — ПРИМЕР РАСЧЁТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Здравоохранение и социальные услуги» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — только расчётная часть с рабочими формулами.</t>
+          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Здравоохранение и социальные услуги» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — расчётная часть с рабочими формулами, уже заполненная цифрами ПРИМЕРА (иллюстративная компания из резюме бизнес-плана, не реальный заёмщик) — чтобы показать порядок величины и логику расчёта. Перед подачей в банк или инвестору замените суммы на данные своего проекта.</t>
         </is>
       </c>
     </row>
@@ -527,10 +534,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
+          <t>Столбец «Сумма, сум» уже заполнен примером расчёта для иллюстративной компании из этого бизнес-плана — на основе рыночных ориентиров 2025-2026 года (там, где источник известен — со ссылкой в комментарии) или экспертной оценки порядка величины (это тоже отмечено). Итоги, прибыль, срок окупаемости и рентабельность ниже пересчитаются автоматически (это формулы). Замените суммы в столбце B на данные вашего собственного проекта — тогда пересчитается всё.</t>
         </is>
       </c>
     </row>
@@ -541,8 +548,9 @@
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
+      <c r="B7" s="6">
+        <f>B16</f>
+        <v/>
       </c>
     </row>
     <row r="8"/>
@@ -555,73 +563,93 @@
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
     </row>
-    <row r="10" ht="21" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Ремонт и оснащение помещения под мед. стандарты</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="21" customHeight="1">
+        <v>850000000</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: ~550 м² в спальном районе Ташкента, капремонт под сан.-эпид. нормы (вентиляция, спецпокрытия, электрика)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Медицинское оборудование</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="21" customHeight="1">
+        <v>900000000</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Пример: УЗИ-аппарат среднего/экспертного класса (Mindray/SonoScape) ~320-380 млн сум (~25-30 тыс.$) + ЭКГ, экспресс-лаборатория, мебель 4 кабинетов — оценка по ценам дилеров СНГ, точных цен по РУз не найдено</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Лицензирование медицинской деятельности</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
+        <v>60000000</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: госпошлины, сан.-эпид. экспертиза, лицензия Минздрава, аккредитация специалистов</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Найм квалифицированного персонала</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr"/>
-    </row>
-    <row r="14" ht="21" customHeight="1">
+        <v>400000000</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: подбор, обучение и аттестация персонала + буферный ФОТ на период запуска до плановой загрузки</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>IT-система учёта пациентов</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+        <v>90000000</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: медицинская информационная система (МИС), компьютеры на ресепшене и в кабинетах</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Страхование профессиональной ответственности</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>часто требуется на этапе лицензирования</t>
+          <t>часто требуется на этапе лицензирования — Пример: годовая премия, уплаченная авансом при запуске — оценка</t>
         </is>
       </c>
     </row>
@@ -647,55 +675,63 @@
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
     </row>
-    <row r="19" ht="21" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Приём и консультации</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="21" customHeight="1">
+        <v>126000000</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Пример: ~700 приёмов/мес (из ~1040 при 40/день, 26 раб. дн.) × ~180 тыс. сум — на основе прайс-листа частных клиник Ташкента (терапевт/невролог/кардиолог 200 тыс., гинеколог 250 тыс.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Диагностические услуги</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="21" customHeight="1">
+        <v>51000000</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Пример: ~320 процедур/мес × ~160 тыс. сум — УЗИ брюшной полости 280 тыс., УЗИ органов 120-150 тыс., по прайс-листам частных клиник</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="51" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Программы / абонементы</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0</v>
+        <v>60000000</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>чек-апы, ведение хронических пациентов</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="21" customHeight="1">
+          <t>чек-апы, ведение хронических пациентов — Пример: оценка: комплексные чек-апы и годовые программы диспансерного наблюдения</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Корпоративные программы для работодателей</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0</v>
+        <v>48000000</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>профилактические осмотры сотрудников</t>
+          <t>профилактические осмотры сотрудников — Пример: оценка: 2-3 контракта с компаниями на периодические медосмотры сотрудников</t>
         </is>
       </c>
     </row>
@@ -721,60 +757,80 @@
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
     </row>
-    <row r="26" ht="21" customHeight="1">
+    <row r="26" ht="81" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>ФОТ врачей и мед. персонала</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
+        <v>78000000</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Пример: главврач-совладелец 15 млн + 4 врача по 10 млн + 2 медсестры по 5 млн + администратор 4,5 млн + ЕСП ~12%; ориентир — зарплата врача в вакансиях Ташкента ~6,9 млн сум (tashkent.gorodrabot.uz), для частной клиники заложено выше среднего</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Расходные материалы и медикаменты</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="21" customHeight="1">
+        <v>18000000</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: гель для УЗИ, расходники, медикаменты — ~6-7% от выручки</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Обслуживание оборудования</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29" ht="21" customHeight="1">
+        <v>7000000</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: сервисный контракт на УЗИ-аппарат и прочее оборудование, ~1% от стоимости в месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="51" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Аренда и коммунальные услуги</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="21" customHeight="1">
+        <v>95000000</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: ~550 м² в спальном районе Ташкента, ~12-15$/м²/мес (для сравнения офисы класса B — 26,4$/м², CMWP/spot.uz) + коммунальные</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Страхование профессиональной ответственности</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr"/>
+        <v>8500000</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Пример: ежемесячный эквивалент годовой премии (~100 млн сум/год)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -811,9 +867,10 @@
         <f>IFERROR(B7/B33,"—")</f>
         <v/>
       </c>
-      <c r="C35" s="9">
-        <f> Начальные инвестиции / Ежемесячная прибыль</f>
-        <v/>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Начальные инвестиции ÷ Ежемесячная прибыль</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -826,24 +883,34 @@
         <f>IFERROR(B33/B23*100,"—")</f>
         <v/>
       </c>
-      <c r="C36" s="9">
-        <f> Ежемесячная прибыль / Выручка × 100%</f>
-        <v/>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Ежемесячная прибыль ÷ Выручка × 100%</t>
+        </is>
       </c>
     </row>
     <row r="37"/>
-    <row r="38" ht="40" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
+    <row r="38" ht="80" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Как считался этот пример: Инвестиции 2,4 млрд сум складываются из ремонта, оборудования (вкл. УЗИ), лицензирования, найма и буферного ФОТ, IT-системы и страхования. При выходе на полную загрузку 40 приёмов/день прибыль ≈78,5 млн сум/мес даёт окупаемость ≈30,6 мес. — совпадает с заявленным ориентиром ~30 мес. (в первые месяцы после открытия загрузка ниже целевой).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40" ht="55" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Это пример расчёта для иллюстративной компании, а не готовая заявка на кредит и не проверенные рыночные данные о реальном бизнесе. Суммы в столбце B — рабочие формулы: замените их на цифры вашего проекта, и итоги, прибыль, срок окупаемости и рентабельность пересчитаются автоматически. Там, где в комментарии указан источник — это ориентир на 2025-2026 год, проверяйте актуальность перед подачей документов в банк; где указана «экспертная оценка» — это иллюстрация порядка величины, а не факт.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A40:C40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
